--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -859,7 +859,7 @@
     <t>0.7602,0.0020,0.2667,0.0003</t>
   </si>
   <si>
-    <t>0.6939,0.0029,0.3240,0.0002</t>
+    <t>0.6940,0.0029,0.3240,0.0002</t>
   </si>
   <si>
     <t>0.3169,0.0135,0.7247,0.0047</t>
@@ -991,7 +991,7 @@
     <t>0.6382,0.0060,0.4447,0.0002</t>
   </si>
   <si>
-    <t>0.3408,0.0013,0.7566,0.0001</t>
+    <t>0.3408,0.0013,0.7567,0.0001</t>
   </si>
   <si>
     <t>0.6688,0.0036,0.2954,0.0003</t>
@@ -1153,7 +1153,7 @@
     <t>0.0024,0.9976,0.0551,0.0000</t>
   </si>
   <si>
-    <t>0.7381,0.3721,0.0237,0.0008</t>
+    <t>0.7381,0.3720,0.0237,0.0008</t>
   </si>
   <si>
     <t>0.1539,0.8057,0.2476,0.0014</t>
@@ -1267,7 +1267,7 @@
     <t>0.0000,0.9930,0.9913,0.0000</t>
   </si>
   <si>
-    <t>0.4039,0.0011,0.6216,0.0004</t>
+    <t>0.4039,0.0011,0.6217,0.0004</t>
   </si>
   <si>
     <t>0.0513,0.5762,0.7997,0.0051</t>
@@ -1324,7 +1324,7 @@
     <t>0.6993,0.0028,0.3562,0.0004</t>
   </si>
   <si>
-    <t>0.4822,0.0012,0.5704,0.0003</t>
+    <t>0.4821,0.0012,0.5704,0.0003</t>
   </si>
   <si>
     <t>0.9347,0.0017,0.0698,0.0002</t>
@@ -1336,7 +1336,7 @@
     <t>0.7892,0.0019,0.2278,0.0005</t>
   </si>
   <si>
-    <t>0.6822,0.0014,0.3329,0.0006</t>
+    <t>0.6822,0.0014,0.3330,0.0006</t>
   </si>
   <si>
     <t>0.8242,0.1005,0.0765,0.0098</t>
@@ -1519,7 +1519,7 @@
     <t>0.7014,0.0018,0.3029,0.0024</t>
   </si>
   <si>
-    <t>0.7619,0.0064,0.2143,0.0007</t>
+    <t>0.7619,0.0064,0.2144,0.0007</t>
   </si>
   <si>
     <t>0.9813,0.0045,0.0066,0.0021</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
   <si>
     <t>Filename</t>
   </si>
@@ -814,6 +814,9 @@
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,0</t>
   </si>
   <si>
@@ -823,76 +826,79 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,0,1,1</t>
   </si>
   <si>
-    <t>0.8029,0.0032,0.1019,0.0148</t>
-  </si>
-  <si>
-    <t>0.0041,0.0010,0.1961,0.9795</t>
-  </si>
-  <si>
-    <t>0.8233,0.0025,0.0294,0.0630</t>
-  </si>
-  <si>
-    <t>0.1285,0.0014,0.3007,0.2581</t>
-  </si>
-  <si>
-    <t>0.8270,0.0036,0.1532,0.0003</t>
-  </si>
-  <si>
-    <t>0.7048,0.0129,0.2351,0.0010</t>
+    <t>0.8030,0.0032,0.1020,0.0148</t>
+  </si>
+  <si>
+    <t>0.0041,0.0010,0.1966,0.9794</t>
+  </si>
+  <si>
+    <t>0.8239,0.0025,0.0294,0.0627</t>
+  </si>
+  <si>
+    <t>0.1288,0.0014,0.3007,0.2571</t>
+  </si>
+  <si>
+    <t>0.8271,0.0036,0.1530,0.0003</t>
+  </si>
+  <si>
+    <t>0.7050,0.0129,0.2349,0.0010</t>
   </si>
   <si>
     <t>0.6978,0.0020,0.3833,0.0002</t>
   </si>
   <si>
-    <t>0.8507,0.0024,0.1524,0.0002</t>
+    <t>0.8506,0.0024,0.1525,0.0002</t>
   </si>
   <si>
     <t>0.9671,0.0091,0.0105,0.0032</t>
   </si>
   <si>
-    <t>0.8177,0.0119,0.1336,0.0014</t>
-  </si>
-  <si>
-    <t>0.7602,0.0020,0.2667,0.0003</t>
-  </si>
-  <si>
-    <t>0.6940,0.0029,0.3240,0.0002</t>
-  </si>
-  <si>
-    <t>0.3169,0.0135,0.7247,0.0047</t>
+    <t>0.8178,0.0119,0.1335,0.0014</t>
+  </si>
+  <si>
+    <t>0.7605,0.0020,0.2664,0.0003</t>
+  </si>
+  <si>
+    <t>0.6938,0.0029,0.3241,0.0002</t>
+  </si>
+  <si>
+    <t>0.3171,0.0135,0.7247,0.0047</t>
   </si>
   <si>
     <t>0.0066,0.0267,0.9901,0.0011</t>
   </si>
   <si>
-    <t>0.0392,0.0010,0.9809,0.0002</t>
+    <t>0.0391,0.0010,0.9810,0.0002</t>
   </si>
   <si>
     <t>0.0114,0.0180,0.9879,0.0006</t>
   </si>
   <si>
-    <t>0.3525,0.0007,0.7750,0.0002</t>
-  </si>
-  <si>
-    <t>0.0077,0.9914,0.1607,0.0001</t>
-  </si>
-  <si>
-    <t>0.0350,0.9591,0.2251,0.0008</t>
-  </si>
-  <si>
-    <t>0.1293,0.8502,0.1513,0.0005</t>
-  </si>
-  <si>
-    <t>0.0507,0.9047,0.3831,0.0023</t>
+    <t>0.3528,0.0007,0.7749,0.0002</t>
+  </si>
+  <si>
+    <t>0.0077,0.9914,0.1606,0.0001</t>
+  </si>
+  <si>
+    <t>0.0350,0.9592,0.2250,0.0008</t>
+  </si>
+  <si>
+    <t>0.1294,0.8502,0.1511,0.0005</t>
+  </si>
+  <si>
+    <t>0.0507,0.9047,0.3834,0.0022</t>
   </si>
   <si>
     <t>0.0032,0.9971,0.0914,0.0000</t>
   </si>
   <si>
-    <t>0.0503,0.0049,0.9577,0.0038</t>
+    <t>0.0503,0.0049,0.9578,0.0038</t>
   </si>
   <si>
     <t>0.0099,0.0105,0.9863,0.0022</t>
@@ -901,7 +907,7 @@
     <t>0.0103,0.0001,0.9959,0.0001</t>
   </si>
   <si>
-    <t>0.0053,0.0040,0.9943,0.0010</t>
+    <t>0.0053,0.0040,0.9944,0.0010</t>
   </si>
   <si>
     <t>0.0061,0.0015,0.9963,0.0003</t>
@@ -913,28 +919,28 @@
     <t>0.0017,0.0004,0.9976,0.0011</t>
   </si>
   <si>
-    <t>0.4170,0.0535,0.5749,0.0021</t>
-  </si>
-  <si>
-    <t>0.7100,0.0372,0.1919,0.0052</t>
+    <t>0.4169,0.0536,0.5746,0.0021</t>
+  </si>
+  <si>
+    <t>0.7099,0.0372,0.1920,0.0052</t>
   </si>
   <si>
     <t>0.0008,0.0001,0.9994,0.0000</t>
   </si>
   <si>
-    <t>0.0028,0.5130,0.9804,0.0005</t>
-  </si>
-  <si>
-    <t>0.3285,0.0016,0.6860,0.0008</t>
-  </si>
-  <si>
-    <t>0.5122,0.0030,0.5807,0.0003</t>
-  </si>
-  <si>
-    <t>0.1494,0.7408,0.3083,0.0019</t>
-  </si>
-  <si>
-    <t>0.0029,0.8448,0.9546,0.0003</t>
+    <t>0.0028,0.5131,0.9804,0.0005</t>
+  </si>
+  <si>
+    <t>0.3286,0.0016,0.6859,0.0008</t>
+  </si>
+  <si>
+    <t>0.5116,0.0030,0.5813,0.0003</t>
+  </si>
+  <si>
+    <t>0.1491,0.7411,0.3084,0.0019</t>
+  </si>
+  <si>
+    <t>0.0029,0.8449,0.9546,0.0003</t>
   </si>
   <si>
     <t>0.0008,0.7924,0.9879,0.0001</t>
@@ -943,13 +949,13 @@
     <t>0.0002,0.0014,0.9992,0.0002</t>
   </si>
   <si>
-    <t>0.0021,0.0575,0.9906,0.0009</t>
-  </si>
-  <si>
-    <t>0.0395,0.0004,0.9645,0.0026</t>
-  </si>
-  <si>
-    <t>0.0011,0.2453,0.9945,0.0002</t>
+    <t>0.0021,0.0576,0.9906,0.0009</t>
+  </si>
+  <si>
+    <t>0.0396,0.0004,0.9645,0.0026</t>
+  </si>
+  <si>
+    <t>0.0011,0.2451,0.9945,0.0002</t>
   </si>
   <si>
     <t>0.0014,0.9914,0.0213,0.0058</t>
@@ -958,7 +964,7 @@
     <t>0.0004,0.0145,0.9985,0.0002</t>
   </si>
   <si>
-    <t>0.0092,0.2551,0.2782,0.6401</t>
+    <t>0.0093,0.2558,0.2783,0.6393</t>
   </si>
   <si>
     <t>0.0002,0.9994,0.0432,0.0000</t>
@@ -967,7 +973,7 @@
     <t>0.0001,0.9990,0.8588,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9995,0.7471,0.0000</t>
+    <t>0.0001,0.9995,0.7472,0.0000</t>
   </si>
   <si>
     <t>0.0002,0.0346,0.9989,0.0002</t>
@@ -985,34 +991,34 @@
     <t>0.0022,0.0006,0.9980,0.0003</t>
   </si>
   <si>
-    <t>0.0085,0.0109,0.9859,0.0019</t>
-  </si>
-  <si>
-    <t>0.6382,0.0060,0.4447,0.0002</t>
-  </si>
-  <si>
-    <t>0.3408,0.0013,0.7567,0.0001</t>
-  </si>
-  <si>
-    <t>0.6688,0.0036,0.2954,0.0003</t>
-  </si>
-  <si>
-    <t>0.0440,0.0014,0.9701,0.0000</t>
-  </si>
-  <si>
-    <t>0.4201,0.0008,0.6752,0.0001</t>
-  </si>
-  <si>
-    <t>0.5612,0.0022,0.5116,0.0002</t>
-  </si>
-  <si>
-    <t>0.6587,0.0011,0.4229,0.0001</t>
+    <t>0.0085,0.0109,0.9859,0.0018</t>
+  </si>
+  <si>
+    <t>0.6383,0.0061,0.4445,0.0002</t>
+  </si>
+  <si>
+    <t>0.3412,0.0013,0.7564,0.0001</t>
+  </si>
+  <si>
+    <t>0.6685,0.0036,0.2959,0.0003</t>
+  </si>
+  <si>
+    <t>0.0441,0.0014,0.9700,0.0000</t>
+  </si>
+  <si>
+    <t>0.4203,0.0008,0.6753,0.0001</t>
+  </si>
+  <si>
+    <t>0.5615,0.0022,0.5114,0.0002</t>
+  </si>
+  <si>
+    <t>0.6591,0.0011,0.4226,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9972,0.9808,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.1147,0.9994,0.0000</t>
+    <t>0.0001,0.1146,0.9994,0.0000</t>
   </si>
   <si>
     <t>0.0005,0.0096,0.9986,0.0003</t>
@@ -1024,16 +1030,16 @@
     <t>0.0000,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0035,0.9949,0.2164,0.0000</t>
+    <t>0.0035,0.9949,0.2163,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9997,0.0020,0.0000</t>
   </si>
   <si>
-    <t>0.6575,0.0015,0.4299,0.0002</t>
-  </si>
-  <si>
-    <t>0.0841,0.0795,0.8923,0.0022</t>
+    <t>0.6578,0.0015,0.4297,0.0002</t>
+  </si>
+  <si>
+    <t>0.0841,0.0796,0.8923,0.0022</t>
   </si>
   <si>
     <t>0.0017,0.0067,0.9979,0.0002</t>
@@ -1045,40 +1051,40 @@
     <t>0.0001,0.9705,0.9962,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9996,0.6639,0.0000</t>
+    <t>0.0001,0.9996,0.6637,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9911,0.9791,0.0000</t>
   </si>
   <si>
-    <t>0.0203,0.0007,0.1522,0.9696</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.0859,0.9967</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.1706,0.9938</t>
-  </si>
-  <si>
-    <t>0.0025,0.0003,0.4346,0.9048</t>
-  </si>
-  <si>
-    <t>0.0180,0.0013,0.3058,0.9094</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.2879,0.9885</t>
+    <t>0.0203,0.0007,0.1526,0.9695</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0860,0.9967</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.1710,0.9938</t>
+  </si>
+  <si>
+    <t>0.0025,0.0003,0.4349,0.9045</t>
+  </si>
+  <si>
+    <t>0.0181,0.0013,0.3063,0.9090</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.2885,0.9885</t>
   </si>
   <si>
     <t>0.0000,0.9966,0.9846,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.7692,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9327,0.9749,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9360,0.9944,0.0000</t>
+    <t>0.0001,0.7695,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9328,0.9749,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9361,0.9944,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9942,0.9936,0.0000</t>
@@ -1087,34 +1093,34 @@
     <t>0.0001,0.9880,0.9813,0.0000</t>
   </si>
   <si>
-    <t>0.9379,0.0032,0.0412,0.0005</t>
-  </si>
-  <si>
-    <t>0.5908,0.0102,0.3978,0.0009</t>
+    <t>0.9378,0.0032,0.0412,0.0005</t>
+  </si>
+  <si>
+    <t>0.5909,0.0102,0.3977,0.0009</t>
   </si>
   <si>
     <t>0.9845,0.0050,0.0034,0.0019</t>
   </si>
   <si>
-    <t>0.7161,0.0353,0.1966,0.0021</t>
-  </si>
-  <si>
-    <t>0.6321,0.0092,0.3778,0.0005</t>
+    <t>0.7159,0.0353,0.1967,0.0021</t>
+  </si>
+  <si>
+    <t>0.6322,0.0092,0.3776,0.0005</t>
   </si>
   <si>
     <t>0.9849,0.0021,0.0046,0.0010</t>
   </si>
   <si>
-    <t>0.4434,0.0019,0.6172,0.0002</t>
-  </si>
-  <si>
-    <t>0.8788,0.0009,0.0353,0.0001</t>
-  </si>
-  <si>
-    <t>0.7041,0.0028,0.2562,0.0006</t>
-  </si>
-  <si>
-    <t>0.9589,0.0066,0.0185,0.0008</t>
+    <t>0.4436,0.0019,0.6171,0.0002</t>
+  </si>
+  <si>
+    <t>0.8790,0.0009,0.0353,0.0001</t>
+  </si>
+  <si>
+    <t>0.7042,0.0028,0.2562,0.0006</t>
+  </si>
+  <si>
+    <t>0.9588,0.0066,0.0185,0.0008</t>
   </si>
   <si>
     <t>0.7652,0.0043,0.2045,0.0008</t>
@@ -1126,13 +1132,13 @@
     <t>0.7489,0.0047,0.1793,0.0011</t>
   </si>
   <si>
-    <t>0.9847,0.0019,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.8961,0.0064,0.0613,0.0012</t>
-  </si>
-  <si>
-    <t>0.6459,0.0045,0.3601,0.0004</t>
+    <t>0.9846,0.0019,0.0045,0.0004</t>
+  </si>
+  <si>
+    <t>0.8963,0.0064,0.0611,0.0012</t>
+  </si>
+  <si>
+    <t>0.6462,0.0046,0.3599,0.0004</t>
   </si>
   <si>
     <t>0.0003,0.0001,0.9997,0.0001</t>
@@ -1141,7 +1147,7 @@
     <t>0.0163,0.0017,0.9899,0.0006</t>
   </si>
   <si>
-    <t>0.8238,0.0005,0.3000,0.0001</t>
+    <t>0.8235,0.0005,0.3005,0.0001</t>
   </si>
   <si>
     <t>0.0222,0.0011,0.9872,0.0005</t>
@@ -1153,19 +1159,19 @@
     <t>0.0024,0.9976,0.0551,0.0000</t>
   </si>
   <si>
-    <t>0.7381,0.3720,0.0237,0.0008</t>
-  </si>
-  <si>
-    <t>0.1539,0.8057,0.2476,0.0014</t>
-  </si>
-  <si>
-    <t>0.0074,0.9934,0.0411,0.0001</t>
+    <t>0.7380,0.3721,0.0237,0.0008</t>
+  </si>
+  <si>
+    <t>0.1537,0.8058,0.2476,0.0014</t>
+  </si>
+  <si>
+    <t>0.0074,0.9934,0.0412,0.0001</t>
   </si>
   <si>
     <t>0.0003,0.9995,0.0252,0.0000</t>
   </si>
   <si>
-    <t>0.3982,0.4220,0.3004,0.0045</t>
+    <t>0.3980,0.4222,0.3004,0.0045</t>
   </si>
   <si>
     <t>0.0457,0.0338,0.9552,0.0034</t>
@@ -1174,34 +1180,34 @@
     <t>0.0064,0.0085,0.9917,0.0010</t>
   </si>
   <si>
-    <t>0.1363,0.0398,0.8537,0.0050</t>
+    <t>0.1360,0.0398,0.8540,0.0050</t>
   </si>
   <si>
     <t>0.0334,0.0292,0.9619,0.0068</t>
   </si>
   <si>
-    <t>0.0009,0.1790,0.9760,0.0087</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.3429,0.0000</t>
+    <t>0.0009,0.1793,0.9760,0.0087</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.3426,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0386,0.0000</t>
   </si>
   <si>
-    <t>0.0017,0.9937,0.1744,0.0021</t>
-  </si>
-  <si>
-    <t>0.0001,0.9986,0.5841,0.0001</t>
-  </si>
-  <si>
-    <t>0.0061,0.9673,0.7187,0.0005</t>
-  </si>
-  <si>
-    <t>0.4610,0.0542,0.4837,0.0006</t>
-  </si>
-  <si>
-    <t>0.1611,0.4902,0.5549,0.0032</t>
+    <t>0.0017,0.9938,0.1748,0.0021</t>
+  </si>
+  <si>
+    <t>0.0001,0.9986,0.5840,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.9673,0.7188,0.0005</t>
+  </si>
+  <si>
+    <t>0.4610,0.0542,0.4835,0.0006</t>
+  </si>
+  <si>
+    <t>0.1611,0.4903,0.5547,0.0032</t>
   </si>
   <si>
     <t>0.7988,0.0006,0.2010,0.0002</t>
@@ -1210,28 +1216,28 @@
     <t>0.9524,0.0091,0.0164,0.0071</t>
   </si>
   <si>
-    <t>0.7759,0.0053,0.1649,0.0018</t>
-  </si>
-  <si>
-    <t>0.6254,0.0027,0.4198,0.0004</t>
+    <t>0.7763,0.0053,0.1647,0.0018</t>
+  </si>
+  <si>
+    <t>0.6258,0.0027,0.4195,0.0004</t>
   </si>
   <si>
     <t>0.9848,0.0009,0.0073,0.0005</t>
   </si>
   <si>
-    <t>0.5523,0.0004,0.4382,0.0003</t>
-  </si>
-  <si>
-    <t>0.4848,0.0014,0.5373,0.0004</t>
-  </si>
-  <si>
-    <t>0.5443,0.0022,0.5047,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9231,0.9848,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.6740,0.9990,0.0000</t>
+    <t>0.5522,0.0004,0.4383,0.0003</t>
+  </si>
+  <si>
+    <t>0.4848,0.0014,0.5375,0.0004</t>
+  </si>
+  <si>
+    <t>0.5446,0.0022,0.5046,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9231,0.9849,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.6739,0.9990,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0064,0.9996,0.0002</t>
@@ -1240,49 +1246,49 @@
     <t>0.0012,0.0860,0.9971,0.0001</t>
   </si>
   <si>
-    <t>0.6115,0.0025,0.4352,0.0023</t>
-  </si>
-  <si>
-    <t>0.2853,0.0778,0.6664,0.0143</t>
+    <t>0.6117,0.0025,0.4352,0.0023</t>
+  </si>
+  <si>
+    <t>0.2857,0.0779,0.6658,0.0143</t>
   </si>
   <si>
     <t>0.0165,0.0003,0.9853,0.0017</t>
   </si>
   <si>
-    <t>0.4930,0.0122,0.5644,0.0038</t>
-  </si>
-  <si>
-    <t>0.0081,0.0002,0.3382,0.8582</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0406,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.1387,0.9976</t>
-  </si>
-  <si>
-    <t>0.0075,0.0001,0.1255,0.9777</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.4039,0.0011,0.6217,0.0004</t>
-  </si>
-  <si>
-    <t>0.0513,0.5762,0.7997,0.0051</t>
-  </si>
-  <si>
-    <t>0.6605,0.0003,0.3991,0.0001</t>
-  </si>
-  <si>
-    <t>0.1108,0.4803,0.6179,0.0021</t>
-  </si>
-  <si>
-    <t>0.9161,0.0010,0.0475,0.0020</t>
-  </si>
-  <si>
-    <t>0.0550,0.0000,0.9647,0.0000</t>
+    <t>0.4931,0.0122,0.5645,0.0038</t>
+  </si>
+  <si>
+    <t>0.0082,0.0002,0.3387,0.8576</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0407,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.1390,0.9975</t>
+  </si>
+  <si>
+    <t>0.0076,0.0001,0.1257,0.9776</t>
+  </si>
+  <si>
+    <t>0.0000,0.9931,0.9913,0.0000</t>
+  </si>
+  <si>
+    <t>0.4037,0.0011,0.6221,0.0004</t>
+  </si>
+  <si>
+    <t>0.0513,0.5763,0.7998,0.0050</t>
+  </si>
+  <si>
+    <t>0.6608,0.0003,0.3989,0.0001</t>
+  </si>
+  <si>
+    <t>0.1107,0.4805,0.6179,0.0021</t>
+  </si>
+  <si>
+    <t>0.9164,0.0010,0.0474,0.0019</t>
+  </si>
+  <si>
+    <t>0.0551,0.0000,0.9647,0.0000</t>
   </si>
   <si>
     <t>0.0898,0.0000,0.9347,0.0000</t>
@@ -1291,82 +1297,82 @@
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.2440,0.0001,0.7383,0.0002</t>
-  </si>
-  <si>
-    <t>0.7926,0.0013,0.1670,0.0005</t>
-  </si>
-  <si>
-    <t>0.6765,0.0094,0.3490,0.0008</t>
-  </si>
-  <si>
-    <t>0.7663,0.0029,0.2382,0.0008</t>
-  </si>
-  <si>
-    <t>0.5111,0.0199,0.4920,0.0036</t>
-  </si>
-  <si>
-    <t>0.1711,0.5584,0.5418,0.0246</t>
-  </si>
-  <si>
-    <t>0.6664,0.0119,0.3862,0.0012</t>
-  </si>
-  <si>
-    <t>0.5904,0.0283,0.3811,0.0020</t>
-  </si>
-  <si>
-    <t>0.8751,0.0037,0.1114,0.0005</t>
+    <t>0.2443,0.0001,0.7381,0.0002</t>
+  </si>
+  <si>
+    <t>0.7927,0.0013,0.1670,0.0005</t>
+  </si>
+  <si>
+    <t>0.6770,0.0094,0.3485,0.0008</t>
+  </si>
+  <si>
+    <t>0.7664,0.0030,0.2382,0.0008</t>
+  </si>
+  <si>
+    <t>0.5109,0.0200,0.4922,0.0036</t>
+  </si>
+  <si>
+    <t>0.1710,0.5591,0.5420,0.0245</t>
+  </si>
+  <si>
+    <t>0.6666,0.0120,0.3858,0.0012</t>
+  </si>
+  <si>
+    <t>0.5903,0.0284,0.3811,0.0020</t>
+  </si>
+  <si>
+    <t>0.8751,0.0037,0.1115,0.0005</t>
   </si>
   <si>
     <t>0.9719,0.0019,0.0097,0.0016</t>
   </si>
   <si>
-    <t>0.6993,0.0028,0.3562,0.0004</t>
-  </si>
-  <si>
-    <t>0.4821,0.0012,0.5704,0.0003</t>
+    <t>0.6997,0.0028,0.3557,0.0004</t>
+  </si>
+  <si>
+    <t>0.4822,0.0012,0.5705,0.0003</t>
   </si>
   <si>
     <t>0.9347,0.0017,0.0698,0.0002</t>
   </si>
   <si>
-    <t>0.8838,0.0038,0.0984,0.0008</t>
-  </si>
-  <si>
-    <t>0.7892,0.0019,0.2278,0.0005</t>
-  </si>
-  <si>
-    <t>0.6822,0.0014,0.3330,0.0006</t>
-  </si>
-  <si>
-    <t>0.8242,0.1005,0.0765,0.0098</t>
-  </si>
-  <si>
-    <t>0.4628,0.3469,0.2390,0.0042</t>
-  </si>
-  <si>
-    <t>0.7549,0.0341,0.1930,0.0014</t>
-  </si>
-  <si>
-    <t>0.2815,0.0015,0.8010,0.0001</t>
-  </si>
-  <si>
-    <t>0.5801,0.0132,0.4208,0.0005</t>
-  </si>
-  <si>
-    <t>0.6532,0.0028,0.4136,0.0003</t>
-  </si>
-  <si>
-    <t>0.5216,0.0048,0.5206,0.0003</t>
-  </si>
-  <si>
-    <t>0.4444,0.0463,0.5288,0.0029</t>
+    <t>0.8839,0.0038,0.0983,0.0008</t>
+  </si>
+  <si>
+    <t>0.7894,0.0019,0.2276,0.0005</t>
+  </si>
+  <si>
+    <t>0.6829,0.0014,0.3324,0.0006</t>
+  </si>
+  <si>
+    <t>0.8241,0.1006,0.0765,0.0098</t>
+  </si>
+  <si>
+    <t>0.4629,0.3470,0.2388,0.0042</t>
+  </si>
+  <si>
+    <t>0.7546,0.0342,0.1933,0.0014</t>
+  </si>
+  <si>
+    <t>0.2812,0.0015,0.8013,0.0001</t>
+  </si>
+  <si>
+    <t>0.5803,0.0132,0.4206,0.0005</t>
+  </si>
+  <si>
+    <t>0.6530,0.0028,0.4140,0.0003</t>
+  </si>
+  <si>
+    <t>0.5213,0.0048,0.5210,0.0003</t>
+  </si>
+  <si>
+    <t>0.4440,0.0464,0.5292,0.0029</t>
   </si>
   <si>
     <t>0.0021,0.0019,0.9988,0.0000</t>
   </si>
   <si>
-    <t>0.6930,0.0024,0.4295,0.0001</t>
+    <t>0.6934,0.0025,0.4290,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9998,0.0000</t>
@@ -1378,7 +1384,7 @@
     <t>0.0024,0.0020,0.9976,0.0003</t>
   </si>
   <si>
-    <t>0.0013,0.2996,0.9924,0.0002</t>
+    <t>0.0013,0.2993,0.9924,0.0002</t>
   </si>
   <si>
     <t>0.0008,0.0010,0.9994,0.0000</t>
@@ -1390,13 +1396,13 @@
     <t>0.0032,0.0005,0.9978,0.0002</t>
   </si>
   <si>
-    <t>0.0406,0.0035,0.9708,0.0012</t>
+    <t>0.0405,0.0035,0.9709,0.0012</t>
   </si>
   <si>
     <t>0.0367,0.0086,0.9654,0.0019</t>
   </si>
   <si>
-    <t>0.3669,0.0742,0.5832,0.0108</t>
+    <t>0.3667,0.0743,0.5834,0.0108</t>
   </si>
   <si>
     <t>0.0121,0.0162,0.9841,0.0024</t>
@@ -1408,40 +1414,40 @@
     <t>0.0115,0.0078,0.9872,0.0011</t>
   </si>
   <si>
-    <t>0.0665,0.0117,0.9389,0.0044</t>
-  </si>
-  <si>
-    <t>0.1444,0.0356,0.8561,0.0012</t>
+    <t>0.0665,0.0118,0.9389,0.0044</t>
+  </si>
+  <si>
+    <t>0.1442,0.0356,0.8563,0.0012</t>
   </si>
   <si>
     <t>0.7607,0.1397,0.0245,0.0008</t>
   </si>
   <si>
-    <t>0.0478,0.8818,0.3829,0.0011</t>
-  </si>
-  <si>
-    <t>0.3775,0.2085,0.3745,0.0021</t>
-  </si>
-  <si>
-    <t>0.4422,0.0240,0.5141,0.0006</t>
-  </si>
-  <si>
-    <t>0.2503,0.1440,0.6345,0.0025</t>
-  </si>
-  <si>
-    <t>0.4441,0.3522,0.1949,0.0038</t>
-  </si>
-  <si>
-    <t>0.7343,0.0024,0.2796,0.0026</t>
-  </si>
-  <si>
-    <t>0.2066,0.0319,0.7551,0.0187</t>
-  </si>
-  <si>
-    <t>0.0315,0.0016,0.9733,0.0023</t>
-  </si>
-  <si>
-    <t>0.2619,0.0019,0.7428,0.0055</t>
+    <t>0.0478,0.8818,0.3831,0.0011</t>
+  </si>
+  <si>
+    <t>0.3773,0.2088,0.3742,0.0021</t>
+  </si>
+  <si>
+    <t>0.4421,0.0241,0.5141,0.0006</t>
+  </si>
+  <si>
+    <t>0.2500,0.1443,0.6346,0.0025</t>
+  </si>
+  <si>
+    <t>0.4441,0.3523,0.1948,0.0038</t>
+  </si>
+  <si>
+    <t>0.7340,0.0024,0.2801,0.0026</t>
+  </si>
+  <si>
+    <t>0.2066,0.0320,0.7552,0.0187</t>
+  </si>
+  <si>
+    <t>0.0315,0.0016,0.9734,0.0023</t>
+  </si>
+  <si>
+    <t>0.2618,0.0019,0.7431,0.0055</t>
   </si>
   <si>
     <t>0.0023,0.0007,0.9977,0.0005</t>
@@ -1459,37 +1465,37 @@
     <t>0.0100,0.0018,0.9935,0.0000</t>
   </si>
   <si>
-    <t>0.6851,0.0006,0.3664,0.0002</t>
-  </si>
-  <si>
-    <t>0.5491,0.0201,0.4468,0.0009</t>
-  </si>
-  <si>
-    <t>0.5108,0.0057,0.4167,0.0019</t>
+    <t>0.6852,0.0006,0.3665,0.0002</t>
+  </si>
+  <si>
+    <t>0.5492,0.0202,0.4467,0.0009</t>
+  </si>
+  <si>
+    <t>0.5110,0.0057,0.4167,0.0019</t>
   </si>
   <si>
     <t>0.9714,0.0049,0.0113,0.0023</t>
   </si>
   <si>
-    <t>0.4219,0.0273,0.5427,0.0018</t>
-  </si>
-  <si>
-    <t>0.4434,0.0374,0.4810,0.0021</t>
-  </si>
-  <si>
-    <t>0.6389,0.0054,0.3458,0.0004</t>
-  </si>
-  <si>
-    <t>0.7640,0.0011,0.2776,0.0001</t>
+    <t>0.4216,0.0273,0.5431,0.0018</t>
+  </si>
+  <si>
+    <t>0.4436,0.0375,0.4806,0.0021</t>
+  </si>
+  <si>
+    <t>0.6395,0.0054,0.3451,0.0004</t>
+  </si>
+  <si>
+    <t>0.7646,0.0011,0.2770,0.0001</t>
   </si>
   <si>
     <t>0.0047,0.0006,0.9968,0.0001</t>
   </si>
   <si>
-    <t>0.0231,0.0075,0.9832,0.0007</t>
-  </si>
-  <si>
-    <t>0.1013,0.0051,0.8873,0.0045</t>
+    <t>0.0231,0.0075,0.9833,0.0007</t>
+  </si>
+  <si>
+    <t>0.1014,0.0051,0.8873,0.0045</t>
   </si>
   <si>
     <t>0.0001,0.0004,0.9999,0.0000</t>
@@ -1507,43 +1513,43 @@
     <t>0.0007,0.0032,0.9988,0.0002</t>
   </si>
   <si>
-    <t>0.0084,0.0488,0.9837,0.0023</t>
-  </si>
-  <si>
-    <t>0.4048,0.0009,0.6012,0.0045</t>
-  </si>
-  <si>
-    <t>0.0999,0.0003,0.8245,0.0242</t>
-  </si>
-  <si>
-    <t>0.7014,0.0018,0.3029,0.0024</t>
-  </si>
-  <si>
-    <t>0.7619,0.0064,0.2144,0.0007</t>
+    <t>0.0084,0.0489,0.9837,0.0023</t>
+  </si>
+  <si>
+    <t>0.4044,0.0009,0.6018,0.0045</t>
+  </si>
+  <si>
+    <t>0.0998,0.0003,0.8250,0.0241</t>
+  </si>
+  <si>
+    <t>0.7011,0.0018,0.3036,0.0024</t>
+  </si>
+  <si>
+    <t>0.7616,0.0064,0.2147,0.0007</t>
   </si>
   <si>
     <t>0.9813,0.0045,0.0066,0.0021</t>
   </si>
   <si>
-    <t>0.8124,0.0090,0.1662,0.0005</t>
-  </si>
-  <si>
-    <t>0.4554,0.0295,0.5005,0.0017</t>
-  </si>
-  <si>
-    <t>0.6231,0.0022,0.3802,0.0002</t>
-  </si>
-  <si>
-    <t>0.7831,0.0149,0.1768,0.0010</t>
+    <t>0.8126,0.0091,0.1659,0.0005</t>
+  </si>
+  <si>
+    <t>0.4552,0.0296,0.5008,0.0017</t>
+  </si>
+  <si>
+    <t>0.6231,0.0022,0.3803,0.0002</t>
+  </si>
+  <si>
+    <t>0.7833,0.0149,0.1765,0.0010</t>
   </si>
   <si>
     <t>0.7635,0.0240,0.1695,0.0018</t>
   </si>
   <si>
-    <t>0.4473,0.0045,0.4753,0.0007</t>
-  </si>
-  <si>
-    <t>0.0023,0.2257,0.9839,0.0007</t>
+    <t>0.4472,0.0045,0.4755,0.0007</t>
+  </si>
+  <si>
+    <t>0.0022,0.2258,0.9839,0.0007</t>
   </si>
   <si>
     <t>0.0004,0.0247,0.9993,0.0000</t>
@@ -1552,37 +1558,37 @@
     <t>0.0005,0.0067,0.9993,0.0001</t>
   </si>
   <si>
-    <t>0.0058,0.0230,0.9875,0.0010</t>
+    <t>0.0058,0.0230,0.9876,0.0010</t>
   </si>
   <si>
     <t>0.0015,0.0008,0.9987,0.0001</t>
   </si>
   <si>
-    <t>0.1006,0.0047,0.7904,0.0353</t>
-  </si>
-  <si>
-    <t>0.0355,0.0062,0.9714,0.0014</t>
+    <t>0.1008,0.0047,0.7904,0.0351</t>
+  </si>
+  <si>
+    <t>0.0354,0.0062,0.9714,0.0014</t>
   </si>
   <si>
     <t>0.0002,0.0003,0.9992,0.0010</t>
   </si>
   <si>
-    <t>0.7065,0.0012,0.1082,0.0308</t>
-  </si>
-  <si>
-    <t>0.0007,0.0020,0.0251,0.9985</t>
-  </si>
-  <si>
-    <t>0.0113,0.0005,0.1986,0.9193</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.5005,0.9793</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0841,0.9990</t>
-  </si>
-  <si>
-    <t>0.2710,0.0312,0.2219,0.2824</t>
+    <t>0.7067,0.0012,0.1082,0.0307</t>
+  </si>
+  <si>
+    <t>0.0007,0.0020,0.0252,0.9985</t>
+  </si>
+  <si>
+    <t>0.0113,0.0005,0.1988,0.9190</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.5010,0.9792</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0843,0.9990</t>
+  </si>
+  <si>
+    <t>0.2715,0.0312,0.2219,0.2814</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +1974,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1982,7 +1988,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1996,7 +2002,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2007,10 +2013,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2024,7 +2030,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2038,7 +2044,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2052,7 +2058,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2066,7 +2072,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2080,7 +2086,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2094,7 +2100,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2108,7 +2114,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2122,7 +2128,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2133,10 +2139,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2147,10 +2153,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2161,10 +2167,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2175,10 +2181,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2189,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2203,10 +2209,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2217,10 +2223,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2231,10 +2237,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2245,10 +2251,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2259,10 +2265,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2273,10 +2279,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2287,10 +2293,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2301,10 +2307,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2315,10 +2321,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2329,10 +2335,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2343,10 +2349,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2357,10 +2363,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2371,10 +2377,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2388,7 +2394,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2399,10 +2405,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2413,10 +2419,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2427,10 +2433,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2441,10 +2447,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2455,10 +2461,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2469,10 +2475,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2483,10 +2489,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2497,10 +2503,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2511,10 +2517,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2525,10 +2531,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2539,10 +2545,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2553,10 +2559,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2567,10 +2573,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,7 +2590,7 @@
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2595,10 +2601,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2609,10 +2615,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2623,10 +2629,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2637,10 +2643,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2651,10 +2657,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2665,10 +2671,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2679,10 +2685,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2693,10 +2699,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2707,10 +2713,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2724,7 +2730,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2735,10 +2741,10 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2752,7 +2758,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2763,10 +2769,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2777,10 +2783,10 @@
         <v>259</v>
       </c>
       <c r="C60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2791,10 +2797,10 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2808,7 +2814,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2819,10 +2825,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2833,10 +2839,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2847,10 +2853,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2861,10 +2867,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2875,10 +2881,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2889,10 +2895,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2903,10 +2909,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2920,7 +2926,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2931,10 +2937,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2945,10 +2951,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2959,10 +2965,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2973,10 +2979,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2987,10 +2993,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3001,10 +3007,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3018,7 +3024,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3032,7 +3038,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3046,7 +3052,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3060,7 +3066,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3074,7 +3080,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3088,7 +3094,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3099,10 +3105,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3113,10 +3119,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3127,10 +3133,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3141,10 +3147,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3155,10 +3161,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3169,10 +3175,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3186,7 +3192,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3200,7 +3206,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3214,7 +3220,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3228,7 +3234,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3242,7 +3248,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3256,7 +3262,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3267,10 +3273,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3284,7 +3290,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3298,7 +3304,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3312,7 +3318,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3326,7 +3332,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3340,7 +3346,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3354,7 +3360,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3368,7 +3374,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3382,7 +3388,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3396,7 +3402,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3407,10 +3413,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3421,10 +3427,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3438,7 +3444,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3449,10 +3455,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3463,10 +3469,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3477,10 +3483,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,7 +3500,7 @@
         <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3505,10 +3511,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3519,10 +3525,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3533,10 +3539,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3547,10 +3553,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3561,10 +3567,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3575,10 +3581,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3589,10 +3595,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3603,10 +3609,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3617,10 +3623,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3631,10 +3637,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3645,10 +3651,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3659,10 +3665,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3673,10 +3679,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3687,10 +3693,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3701,10 +3707,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3715,10 +3721,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3732,7 +3738,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3746,7 +3752,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3760,7 +3766,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3774,7 +3780,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3788,7 +3794,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3802,7 +3808,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3813,10 +3819,10 @@
         <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D134" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3827,10 +3833,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D135" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3841,10 +3847,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3855,10 +3861,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3869,10 +3875,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D138" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3883,10 +3889,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3900,7 +3906,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3911,10 +3917,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D141" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3925,10 +3931,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3939,10 +3945,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D143" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3956,7 +3962,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3970,7 +3976,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3984,7 +3990,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3998,7 +4004,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4009,10 +4015,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4023,10 +4029,10 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4037,10 +4043,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D150" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4054,7 +4060,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4065,10 +4071,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4082,7 +4088,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4093,10 +4099,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4107,10 +4113,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4121,10 +4127,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4135,10 +4141,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D157" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4152,7 +4158,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,7 +4172,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4180,7 +4186,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4194,7 +4200,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4205,10 +4211,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D162" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4222,7 +4228,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4236,7 +4242,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4250,7 +4256,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4264,7 +4270,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4278,7 +4284,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4289,10 +4295,10 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D168" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4306,7 +4312,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4320,7 +4326,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4334,7 +4340,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4348,7 +4354,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,7 +4368,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4373,10 +4379,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4390,7 +4396,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4401,10 +4407,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D176" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4418,7 +4424,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,7 +4438,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4443,10 +4449,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D179" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4457,10 +4463,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4471,10 +4477,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D181" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4488,7 +4494,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4499,10 +4505,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D183" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4513,10 +4519,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D184" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4527,10 +4533,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D185" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4541,10 +4547,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D186" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4555,10 +4561,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4569,10 +4575,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D188" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4583,10 +4589,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4597,10 +4603,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4611,10 +4617,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D191" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4625,10 +4631,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D192" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4639,10 +4645,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D193" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4653,10 +4659,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D194" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4667,10 +4673,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4681,10 +4687,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D196" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4695,10 +4701,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D197" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,7 +4718,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4723,10 +4729,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4737,10 +4743,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D200" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4751,10 +4757,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D201" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4765,10 +4771,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4779,10 +4785,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4796,7 +4802,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4807,10 +4813,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D205" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4821,10 +4827,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D206" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4835,10 +4841,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4849,10 +4855,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D208" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4863,10 +4869,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D209" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4877,10 +4883,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4891,10 +4897,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D211" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4905,10 +4911,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4922,7 +4928,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4936,7 +4942,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4950,7 +4956,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4964,7 +4970,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4975,10 +4981,10 @@
         <v>259</v>
       </c>
       <c r="C217" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D217" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4989,10 +4995,10 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D218" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5006,7 +5012,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5020,7 +5026,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5031,10 +5037,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D221" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5045,10 +5051,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D222" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5059,10 +5065,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D223" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5073,10 +5079,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5087,10 +5093,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D225" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5101,10 +5107,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D226" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5115,10 +5121,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5129,10 +5135,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5143,10 +5149,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D229" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5157,10 +5163,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D230" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5171,10 +5177,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5185,10 +5191,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D232" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5199,10 +5205,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D233" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5216,7 +5222,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5230,7 +5236,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5244,7 +5250,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5258,7 +5264,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5269,10 +5275,10 @@
         <v>259</v>
       </c>
       <c r="C238" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D238" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5286,7 +5292,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5300,7 +5306,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5314,7 +5320,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5325,10 +5331,10 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D242" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5339,10 +5345,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5353,10 +5359,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5367,10 +5373,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D245" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5381,10 +5387,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D246" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5395,10 +5401,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D247" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5409,10 +5415,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D248" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5423,10 +5429,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D249" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5437,10 +5443,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5454,7 +5460,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5468,7 +5474,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5482,7 +5488,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5493,10 +5499,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D254" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5510,7 +5516,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5521,10 +5527,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D256" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
